--- a/HotGuy/Assets/Config/Excel/ScoreConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/ScoreConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448C4CC0-929B-4815-AFD2-A059B36F77E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0B99A5-A574-4C65-9E03-9CF220CFBF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConstConfig" sheetId="1" r:id="rId1"/>
@@ -638,10 +638,10 @@
         <v>-15</v>
       </c>
       <c r="F4" s="3">
-        <v>-50</v>
+        <v>-10</v>
       </c>
       <c r="G4" s="3">
-        <v>-100</v>
+        <v>-30</v>
       </c>
       <c r="H4" s="3">
         <v>1.5</v>
